--- a/web/public/ASML_DCF_Model.xlsx
+++ b/web/public/ASML_DCF_Model.xlsx
@@ -13229,7 +13229,7 @@
     <row r="4">
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Table 1: WACC vs terminal growth (Gordon Growth method)</t>
+          <t>Table 1: WACC vs terminal growth (Gordon Growth method; g changes the perpetuity only, FY31-35 fade path held at base)</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
